--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -73,24 +73,12 @@
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
@@ -511,6 +499,12 @@
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5706</t>
   </si>
   <si>
@@ -1357,6 +1351,12 @@
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">3201</t>
   </si>
   <si>
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:27</t>
+    <t xml:space="preserve">2026-09-09 20:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2678,7 +2678,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6.89</v>
+        <v>6.08</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -2689,16 +2689,16 @@
         <v>2018</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -2710,7 +2710,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6.08</v>
+        <v>5.26</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2727,10 +2727,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2742,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>5.12</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2753,10 +2753,10 @@
         <v>2018</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>25</v>
@@ -2774,7 +2774,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5.26</v>
+        <v>4.77</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2785,10 +2785,10 @@
         <v>2018</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
@@ -2806,7 +2806,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5.12</v>
+        <v>4.44</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2817,10 +2817,10 @@
         <v>2018</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -2838,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4.77</v>
+        <v>3.82</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2852,7 +2852,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2870,7 +2870,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4.44</v>
+        <v>3.35</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2881,10 +2881,10 @@
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
@@ -2902,7 +2902,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3.82</v>
+        <v>2.97</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2916,7 +2916,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
@@ -2934,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2966,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2977,10 +2977,10 @@
         <v>2018</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2998,7 +2998,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -3009,10 +3009,10 @@
         <v>2018</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -3041,10 +3041,10 @@
         <v>2018</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>43</v>
@@ -3062,7 +3062,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3073,28 +3073,28 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.64</v>
+        <v>7.47</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3105,28 +3105,28 @@
         <v>2018</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3140,25 +3140,25 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7.47</v>
+        <v>6.28</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3169,28 +3169,28 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6.31</v>
+        <v>6.1</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3204,25 +3204,25 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.28</v>
+        <v>6.02</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3236,7 +3236,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>60</v>
@@ -3245,16 +3245,16 @@
         <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6.1</v>
+        <v>5.68</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3268,7 +3268,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>62</v>
@@ -3277,16 +3277,16 @@
         <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6.02</v>
+        <v>5.68</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3300,7 +3300,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
@@ -3309,16 +3309,16 @@
         <v>65</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3329,28 +3329,28 @@
         <v>2018</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3364,25 +3364,25 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5.65</v>
+        <v>5.58</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3396,7 +3396,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3405,16 +3405,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3425,10 +3425,10 @@
         <v>2018</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3437,16 +3437,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5.58</v>
+        <v>5.37</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3457,10 +3457,10 @@
         <v>2018</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3469,16 +3469,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5.44</v>
+        <v>5.33</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3489,10 +3489,10 @@
         <v>2018</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3501,16 +3501,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3524,7 +3524,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3533,16 +3533,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3553,10 +3553,10 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3565,16 +3565,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5.32</v>
+        <v>5.22</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3585,10 +3585,10 @@
         <v>2018</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3597,16 +3597,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3617,10 +3617,10 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3629,16 +3629,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5.22</v>
+        <v>5.08</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3649,10 +3649,10 @@
         <v>2018</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3661,16 +3661,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5.21</v>
+        <v>5.04</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3681,28 +3681,28 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3716,25 +3716,25 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3745,10 +3745,10 @@
         <v>2018</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3757,16 +3757,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3777,10 +3777,10 @@
         <v>2018</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3789,16 +3789,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3809,10 +3809,10 @@
         <v>2018</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3821,16 +3821,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3844,7 +3844,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3853,16 +3853,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5.01</v>
+        <v>4.98</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3876,7 +3876,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3885,16 +3885,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3905,10 +3905,10 @@
         <v>2018</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3917,16 +3917,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>4.98</v>
+        <v>4.95</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3937,10 +3937,10 @@
         <v>2018</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3949,16 +3949,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3969,10 +3969,10 @@
         <v>2018</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3981,16 +3981,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -4001,10 +4001,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -4013,16 +4013,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -4033,10 +4033,10 @@
         <v>2018</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4045,16 +4045,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4065,10 +4065,10 @@
         <v>2018</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4077,16 +4077,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4097,10 +4097,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4109,16 +4109,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4132,7 +4132,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4141,16 +4141,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4161,10 +4161,10 @@
         <v>2018</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4173,16 +4173,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4193,10 +4193,10 @@
         <v>2018</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4205,16 +4205,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4225,10 +4225,10 @@
         <v>2018</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -4237,16 +4237,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4257,10 +4257,10 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4269,16 +4269,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4289,10 +4289,10 @@
         <v>2018</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4301,10 +4301,10 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4321,10 +4321,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4333,16 +4333,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4353,10 +4353,10 @@
         <v>2018</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4365,16 +4365,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4385,10 +4385,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4397,16 +4397,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4417,10 +4417,10 @@
         <v>2018</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4429,16 +4429,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4452,7 +4452,7 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4461,16 +4461,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4484,7 +4484,7 @@
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4493,16 +4493,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4516,7 +4516,7 @@
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4525,16 +4525,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4545,10 +4545,10 @@
         <v>2018</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4557,16 +4557,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4577,10 +4577,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4589,16 +4589,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4612,7 +4612,7 @@
         <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4621,16 +4621,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4641,10 +4641,10 @@
         <v>2018</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4653,16 +4653,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4673,10 +4673,10 @@
         <v>2018</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4685,16 +4685,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4705,10 +4705,10 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4717,16 +4717,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4737,10 +4737,10 @@
         <v>2018</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4749,16 +4749,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4769,10 +4769,10 @@
         <v>2018</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4781,16 +4781,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4801,10 +4801,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4813,16 +4813,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4836,7 +4836,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4845,16 +4845,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4865,10 +4865,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4877,16 +4877,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4897,10 +4897,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4909,16 +4909,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4932,7 +4932,7 @@
         <v>13</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4941,16 +4941,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4964,7 +4964,7 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4973,10 +4973,10 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4993,10 +4993,10 @@
         <v>2018</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -5005,16 +5005,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -5028,7 +5028,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -5037,10 +5037,10 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5057,10 +5057,10 @@
         <v>2018</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5069,16 +5069,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5092,7 +5092,7 @@
         <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5101,16 +5101,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5121,10 +5121,10 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5133,16 +5133,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5153,10 +5153,10 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5165,16 +5165,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5185,10 +5185,10 @@
         <v>2018</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5197,10 +5197,10 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5217,10 +5217,10 @@
         <v>2018</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5229,16 +5229,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5249,10 +5249,10 @@
         <v>2018</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5261,16 +5261,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5281,10 +5281,10 @@
         <v>2018</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5293,16 +5293,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5313,10 +5313,10 @@
         <v>2018</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5325,10 +5325,10 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5345,10 +5345,10 @@
         <v>2018</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5357,16 +5357,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5380,7 +5380,7 @@
         <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5389,16 +5389,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5409,10 +5409,10 @@
         <v>2018</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5421,10 +5421,10 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5441,10 +5441,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5453,16 +5453,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5473,10 +5473,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5485,16 +5485,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5505,10 +5505,10 @@
         <v>2018</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5517,16 +5517,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5540,7 +5540,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5549,16 +5549,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5569,10 +5569,10 @@
         <v>2018</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5581,16 +5581,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5601,10 +5601,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5613,10 +5613,10 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5633,10 +5633,10 @@
         <v>2018</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5645,16 +5645,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5665,10 +5665,10 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5677,16 +5677,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5697,10 +5697,10 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5709,16 +5709,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5732,7 +5732,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5741,16 +5741,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5761,10 +5761,10 @@
         <v>2018</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5773,16 +5773,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5793,10 +5793,10 @@
         <v>2018</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5805,16 +5805,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5828,7 +5828,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5837,10 +5837,10 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5857,10 +5857,10 @@
         <v>2018</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5869,16 +5869,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5889,10 +5889,10 @@
         <v>2018</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5901,16 +5901,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5921,10 +5921,10 @@
         <v>2018</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5933,16 +5933,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5956,7 +5956,7 @@
         <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5965,10 +5965,10 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5985,10 +5985,10 @@
         <v>2018</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5997,10 +5997,10 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -6017,10 +6017,10 @@
         <v>2018</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6029,16 +6029,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6052,7 +6052,7 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6061,16 +6061,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6084,7 +6084,7 @@
         <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6093,10 +6093,10 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6113,10 +6113,10 @@
         <v>2018</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6125,10 +6125,10 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6145,10 +6145,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6157,16 +6157,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6177,10 +6177,10 @@
         <v>2018</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6189,16 +6189,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6209,10 +6209,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6221,10 +6221,10 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6241,10 +6241,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6253,16 +6253,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6273,10 +6273,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6285,10 +6285,10 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6305,10 +6305,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6317,16 +6317,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6337,10 +6337,10 @@
         <v>2018</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6349,16 +6349,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6369,10 +6369,10 @@
         <v>2018</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6381,16 +6381,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6401,10 +6401,10 @@
         <v>2018</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6413,10 +6413,10 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6433,10 +6433,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6445,16 +6445,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6465,10 +6465,10 @@
         <v>2018</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6477,16 +6477,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6500,7 +6500,7 @@
         <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6509,10 +6509,10 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6532,7 +6532,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6541,16 +6541,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6561,10 +6561,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6573,16 +6573,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6593,10 +6593,10 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6605,16 +6605,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6628,7 +6628,7 @@
         <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6637,16 +6637,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6657,10 +6657,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6669,16 +6669,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6692,7 +6692,7 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6701,16 +6701,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6721,10 +6721,10 @@
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6733,10 +6733,10 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6753,10 +6753,10 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6765,16 +6765,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6785,10 +6785,10 @@
         <v>2018</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6797,10 +6797,10 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6817,10 +6817,10 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6829,16 +6829,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6852,7 +6852,7 @@
         <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6861,10 +6861,10 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6881,10 +6881,10 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6893,16 +6893,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6913,10 +6913,10 @@
         <v>2018</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6925,16 +6925,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6945,10 +6945,10 @@
         <v>2018</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6957,16 +6957,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6977,10 +6977,10 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6989,16 +6989,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -7009,10 +7009,10 @@
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7021,10 +7021,10 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7041,10 +7041,10 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7053,16 +7053,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7076,7 +7076,7 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7085,10 +7085,10 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7105,10 +7105,10 @@
         <v>2018</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7117,16 +7117,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7137,10 +7137,10 @@
         <v>2018</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7149,16 +7149,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7169,10 +7169,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7181,10 +7181,10 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7201,10 +7201,10 @@
         <v>2018</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7213,16 +7213,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7233,10 +7233,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7245,16 +7245,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7265,10 +7265,10 @@
         <v>2018</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7277,16 +7277,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7300,7 +7300,7 @@
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7309,16 +7309,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7332,7 +7332,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7341,16 +7341,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7361,10 +7361,10 @@
         <v>2018</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7373,10 +7373,10 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7396,7 +7396,7 @@
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7405,10 +7405,10 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7425,10 +7425,10 @@
         <v>2018</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7437,16 +7437,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7457,10 +7457,10 @@
         <v>2018</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7469,10 +7469,10 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7492,7 +7492,7 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7501,16 +7501,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7521,10 +7521,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7533,16 +7533,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7553,10 +7553,10 @@
         <v>2018</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7565,10 +7565,10 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7585,10 +7585,10 @@
         <v>2018</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7597,16 +7597,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7617,10 +7617,10 @@
         <v>2018</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7629,16 +7629,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7649,10 +7649,10 @@
         <v>2018</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7661,16 +7661,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7681,10 +7681,10 @@
         <v>2018</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7693,16 +7693,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7713,10 +7713,10 @@
         <v>2018</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7725,10 +7725,10 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7745,10 +7745,10 @@
         <v>2018</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7757,16 +7757,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7777,10 +7777,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7789,10 +7789,10 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7809,10 +7809,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7821,16 +7821,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7844,7 +7844,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7853,16 +7853,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7876,7 +7876,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7885,16 +7885,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7905,28 +7905,28 @@
         <v>2018</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>355</v>
+        <v>45</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7937,28 +7937,28 @@
         <v>2018</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D169" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7969,10 +7969,10 @@
         <v>2018</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7981,16 +7981,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -8004,7 +8004,7 @@
         <v>7</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8013,16 +8013,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -8033,10 +8033,10 @@
         <v>2018</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8045,16 +8045,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8068,7 +8068,7 @@
         <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8077,10 +8077,10 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8097,10 +8097,10 @@
         <v>2018</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8109,16 +8109,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8129,10 +8129,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8141,16 +8141,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8161,10 +8161,10 @@
         <v>2018</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8173,16 +8173,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8196,7 +8196,7 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8205,16 +8205,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8225,10 +8225,10 @@
         <v>2018</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8237,10 +8237,10 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8257,10 +8257,10 @@
         <v>2018</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8269,16 +8269,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8289,10 +8289,10 @@
         <v>2018</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8301,16 +8301,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8324,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8333,16 +8333,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8353,10 +8353,10 @@
         <v>2018</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8365,16 +8365,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8388,7 +8388,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8397,10 +8397,10 @@
         <v>384</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8420,7 +8420,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8429,16 +8429,16 @@
         <v>386</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8449,10 +8449,10 @@
         <v>2018</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8461,16 +8461,16 @@
         <v>388</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8481,10 +8481,10 @@
         <v>2018</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>389</v>
@@ -8493,16 +8493,16 @@
         <v>390</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8513,10 +8513,10 @@
         <v>2018</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8525,16 +8525,16 @@
         <v>392</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8548,7 +8548,7 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8557,16 +8557,16 @@
         <v>394</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8577,28 +8577,28 @@
         <v>2018</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>54</v>
+        <v>395</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>53</v>
+        <v>399</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>1</v>
+        <v>7.68</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8612,25 +8612,25 @@
         <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="G190" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>7.68</v>
+        <v>6.19</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8641,28 +8641,28 @@
         <v>2018</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8673,28 +8673,28 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8705,10 +8705,10 @@
         <v>2018</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>408</v>
@@ -8717,16 +8717,16 @@
         <v>409</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>6.12</v>
+        <v>5.75</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8737,28 +8737,28 @@
         <v>2018</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>5.75</v>
+        <v>5.66</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8769,10 +8769,10 @@
         <v>2018</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>413</v>
@@ -8781,16 +8781,16 @@
         <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>5.66</v>
+        <v>5.42</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8801,28 +8801,28 @@
         <v>2018</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>5.42</v>
+        <v>5.39</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8836,7 +8836,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
@@ -8845,16 +8845,16 @@
         <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8865,10 +8865,10 @@
         <v>2018</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8877,16 +8877,16 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>5.31</v>
+        <v>5.22</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8900,7 +8900,7 @@
         <v>2</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8909,16 +8909,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8929,10 +8929,10 @@
         <v>2018</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
@@ -8941,16 +8941,16 @@
         <v>425</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>5.17</v>
+        <v>5.13</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8961,10 +8961,10 @@
         <v>2018</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>426</v>
@@ -8973,16 +8973,16 @@
         <v>427</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>5.13</v>
+        <v>4.77</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8993,10 +8993,10 @@
         <v>2018</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>428</v>
@@ -9005,16 +9005,16 @@
         <v>429</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -9025,28 +9025,28 @@
         <v>2018</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>430</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>4.75</v>
+        <v>4.29</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9057,28 +9057,28 @@
         <v>2018</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E204" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="F204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9089,10 +9089,10 @@
         <v>2018</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -9101,16 +9101,16 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>4.27</v>
+        <v>4.04</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9121,10 +9121,10 @@
         <v>2018</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9133,16 +9133,16 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>4.04</v>
+        <v>3.93</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9153,10 +9153,10 @@
         <v>2018</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9165,16 +9165,16 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9185,28 +9185,28 @@
         <v>2018</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>440</v>
+        <v>402</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9217,28 +9217,28 @@
         <v>2018</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="E209" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="F209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -9249,10 +9249,10 @@
         <v>2018</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>442</v>
@@ -9261,16 +9261,16 @@
         <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -9284,7 +9284,7 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9293,16 +9293,16 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -9316,7 +9316,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9325,10 +9325,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9348,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9357,10 +9357,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9380,7 +9380,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9389,10 +9389,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9412,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9421,10 +9421,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9444,7 +9444,7 @@
         <v>2</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9453,10 +9453,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9476,7 +9476,7 @@
         <v>3</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9485,10 +9485,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9508,7 +9508,7 @@
         <v>15</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9517,10 +9517,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9540,7 +9540,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9549,10 +9549,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9572,7 +9572,7 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9581,10 +9581,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9604,7 +9604,7 @@
         <v>3</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9613,10 +9613,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9636,7 +9636,7 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9645,10 +9645,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9668,7 +9668,7 @@
         <v>4</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9677,10 +9677,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9700,7 +9700,7 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
@@ -9709,10 +9709,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9732,7 +9732,7 @@
         <v>3</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>472</v>
@@ -9741,10 +9741,10 @@
         <v>473</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9764,7 +9764,7 @@
         <v>3</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>474</v>
@@ -9773,10 +9773,10 @@
         <v>475</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9796,7 +9796,7 @@
         <v>4</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>476</v>
@@ -9805,10 +9805,10 @@
         <v>477</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9828,7 +9828,7 @@
         <v>4</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>478</v>
@@ -9837,10 +9837,10 @@
         <v>479</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9860,7 +9860,7 @@
         <v>15</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>480</v>
@@ -9869,10 +9869,10 @@
         <v>481</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9892,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>482</v>
@@ -9901,10 +9901,10 @@
         <v>483</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -397,18 +397,18 @@
     <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
+    <t xml:space="preserve">16106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinto</t>
+  </si>
+  <si>
     <t xml:space="preserve">16204</t>
   </si>
   <si>
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
-    <t xml:space="preserve">16106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinto</t>
-  </si>
-  <si>
     <t xml:space="preserve">5802</t>
   </si>
   <si>
@@ -685,18 +685,18 @@
     <t xml:space="preserve">Paine</t>
   </si>
   <si>
+    <t xml:space="preserve">5303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
     <t xml:space="preserve">5402</t>
   </si>
   <si>
     <t xml:space="preserve">Cabildo</t>
   </si>
   <si>
-    <t xml:space="preserve">5303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
     <t xml:space="preserve">13110</t>
   </si>
   <si>
@@ -709,18 +709,18 @@
     <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
+    <t xml:space="preserve">13119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
     <t xml:space="preserve">13301</t>
   </si>
   <si>
     <t xml:space="preserve">Colina</t>
   </si>
   <si>
-    <t xml:space="preserve">13119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
     <t xml:space="preserve">16103</t>
   </si>
   <si>
@@ -877,18 +877,18 @@
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
+    <t xml:space="preserve">16104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
     <t xml:space="preserve">16202</t>
   </si>
   <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
-    <t xml:space="preserve">16104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
     <t xml:space="preserve">7101</t>
   </si>
   <si>
@@ -1102,18 +1102,18 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">6103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
     <t xml:space="preserve">6302</t>
   </si>
   <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
-    <t xml:space="preserve">6103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinco</t>
-  </si>
-  <si>
     <t xml:space="preserve">7307</t>
   </si>
   <si>
@@ -1162,18 +1162,18 @@
     <t xml:space="preserve">Treguaco</t>
   </si>
   <si>
+    <t xml:space="preserve">13120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">13403</t>
   </si>
   <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
-    <t xml:space="preserve">13120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">13114</t>
   </si>
   <si>
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:21</t>
+    <t xml:space="preserve">2026-09-18 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2018.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">metric_label</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11102</t>
@@ -76,9 +76,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -196,7 +193,7 @@
     <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5105</t>
@@ -274,9 +271,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">13116</t>
   </si>
   <si>
@@ -295,7 +289,7 @@
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16303</t>
@@ -955,7 +949,7 @@
     <t xml:space="preserve">16206</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">13605</t>
@@ -1213,7 +1207,7 @@
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1404</t>
@@ -1480,7 +1474,7 @@
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8314</t>
@@ -1516,7 +1510,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9210</t>
@@ -1567,7 +1561,7 @@
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14203</t>
@@ -1627,7 +1621,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">10103</t>
@@ -1987,7 +1981,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">8102</t>
@@ -2143,7 +2137,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:32</t>
+    <t xml:space="preserve">2026-10-05 18:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2675,7 +2669,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -2704,10 +2698,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -2736,10 +2730,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2765,13 +2759,13 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2800,10 +2794,10 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2832,10 +2826,10 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2861,13 +2855,13 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2893,13 +2887,13 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2925,13 +2919,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2960,10 +2954,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2989,13 +2983,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -3024,10 +3018,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3056,10 +3050,10 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3085,13 +3079,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3117,13 +3111,13 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -3149,19 +3143,19 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3181,19 +3175,19 @@
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3213,19 +3207,19 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3245,19 +3239,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3277,19 +3271,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3309,19 +3303,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3341,19 +3335,19 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3373,19 +3367,19 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3405,19 +3399,19 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3437,19 +3431,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3469,19 +3463,19 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3501,19 +3495,19 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3533,19 +3527,19 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3565,19 +3559,19 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3597,19 +3591,19 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3629,19 +3623,19 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3661,19 +3655,19 @@
         <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3693,19 +3687,19 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3725,19 +3719,19 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3757,19 +3751,19 @@
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3789,19 +3783,19 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3821,19 +3815,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3853,19 +3847,19 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3885,19 +3879,19 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3917,19 +3911,19 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3949,19 +3943,19 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3981,19 +3975,19 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -4013,19 +4007,19 @@
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4045,19 +4039,19 @@
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4077,19 +4071,19 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4109,19 +4103,19 @@
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4141,19 +4135,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4173,19 +4167,19 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4205,19 +4199,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4237,19 +4231,19 @@
         <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4269,19 +4263,19 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4301,19 +4295,19 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4333,19 +4327,19 @@
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4365,19 +4359,19 @@
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4397,19 +4391,19 @@
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4429,19 +4423,19 @@
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4461,19 +4455,19 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4493,19 +4487,19 @@
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4525,19 +4519,19 @@
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4557,19 +4551,19 @@
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4589,19 +4583,19 @@
         <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4621,19 +4615,19 @@
         <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4653,19 +4647,19 @@
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4685,19 +4679,19 @@
         <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4717,19 +4711,19 @@
         <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4749,19 +4743,19 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4781,19 +4775,19 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4813,19 +4807,19 @@
         <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4845,19 +4839,19 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4877,19 +4871,19 @@
         <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4909,19 +4903,19 @@
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4941,19 +4935,19 @@
         <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4973,19 +4967,19 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -5005,19 +4999,19 @@
         <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -5037,19 +5031,19 @@
         <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5069,19 +5063,19 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5101,19 +5095,19 @@
         <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5133,19 +5127,19 @@
         <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5165,19 +5159,19 @@
         <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5197,19 +5191,19 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5229,19 +5223,19 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5261,19 +5255,19 @@
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5293,19 +5287,19 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5325,19 +5319,19 @@
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5357,19 +5351,19 @@
         <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5389,19 +5383,19 @@
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5421,19 +5415,19 @@
         <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5453,19 +5447,19 @@
         <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5485,19 +5479,19 @@
         <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5517,19 +5511,19 @@
         <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5549,19 +5543,19 @@
         <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5581,19 +5575,19 @@
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5613,19 +5607,19 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5645,19 +5639,19 @@
         <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5677,19 +5671,19 @@
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5709,19 +5703,19 @@
         <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5741,19 +5735,19 @@
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5773,19 +5767,19 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5805,19 +5799,19 @@
         <v>6</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5837,19 +5831,19 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5869,19 +5863,19 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5901,19 +5895,19 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5933,19 +5927,19 @@
         <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5965,19 +5959,19 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5997,19 +5991,19 @@
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -6029,19 +6023,19 @@
         <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6061,19 +6055,19 @@
         <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6093,19 +6087,19 @@
         <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6125,19 +6119,19 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6157,19 +6151,19 @@
         <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6189,19 +6183,19 @@
         <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6221,19 +6215,19 @@
         <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6253,19 +6247,19 @@
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6285,19 +6279,19 @@
         <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6317,19 +6311,19 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6349,19 +6343,19 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6381,19 +6375,19 @@
         <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6413,19 +6407,19 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6445,19 +6439,19 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6477,19 +6471,19 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6509,19 +6503,19 @@
         <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6541,19 +6535,19 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6573,19 +6567,19 @@
         <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6605,19 +6599,19 @@
         <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6637,19 +6631,19 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6669,19 +6663,19 @@
         <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6701,19 +6695,19 @@
         <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6733,19 +6727,19 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6765,19 +6759,19 @@
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6797,19 +6791,19 @@
         <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6829,19 +6823,19 @@
         <v>6</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6861,19 +6855,19 @@
         <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6893,19 +6887,19 @@
         <v>16</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6925,19 +6919,19 @@
         <v>16</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6957,19 +6951,19 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6989,19 +6983,19 @@
         <v>16</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -7021,19 +7015,19 @@
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7053,19 +7047,19 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7085,19 +7079,19 @@
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7117,19 +7111,19 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7149,19 +7143,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7181,19 +7175,19 @@
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7213,19 +7207,19 @@
         <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7245,19 +7239,19 @@
         <v>16</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7277,19 +7271,19 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7309,19 +7303,19 @@
         <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7341,19 +7335,19 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7373,19 +7367,19 @@
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7405,19 +7399,19 @@
         <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7437,19 +7431,19 @@
         <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7469,19 +7463,19 @@
         <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7501,19 +7495,19 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7533,19 +7527,19 @@
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7565,19 +7559,19 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7597,19 +7591,19 @@
         <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7629,19 +7623,19 @@
         <v>16</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7661,19 +7655,19 @@
         <v>6</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7693,19 +7687,19 @@
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7725,19 +7719,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7757,19 +7751,19 @@
         <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7789,19 +7783,19 @@
         <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7821,19 +7815,19 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7853,19 +7847,19 @@
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7885,19 +7879,19 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7917,19 +7911,19 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7949,19 +7943,19 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7981,19 +7975,19 @@
         <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -8013,19 +8007,19 @@
         <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8045,19 +8039,19 @@
         <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8077,19 +8071,19 @@
         <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8109,19 +8103,19 @@
         <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8141,19 +8135,19 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8173,19 +8167,19 @@
         <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8205,19 +8199,19 @@
         <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8237,19 +8231,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8269,19 +8263,19 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8301,19 +8295,19 @@
         <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8333,19 +8327,19 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8365,19 +8359,19 @@
         <v>16</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8397,19 +8391,19 @@
         <v>16</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8429,19 +8423,19 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8461,19 +8455,19 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8493,19 +8487,19 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8525,19 +8519,19 @@
         <v>6</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8557,19 +8551,19 @@
         <v>5</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8589,19 +8583,19 @@
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8621,19 +8615,19 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8653,19 +8647,19 @@
         <v>1</v>
       </c>
       <c r="C191" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="F191" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E191" s="2" t="s">
+      <c r="G191" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8685,19 +8679,19 @@
         <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8717,19 +8711,19 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D193" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="F193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8749,19 +8743,19 @@
         <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D194" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="F194" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8781,19 +8775,19 @@
         <v>1</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8813,19 +8807,19 @@
         <v>15</v>
       </c>
       <c r="C196" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D196" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="F196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8845,19 +8839,19 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8877,19 +8871,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="F198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8909,19 +8903,19 @@
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8941,19 +8935,19 @@
         <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8973,19 +8967,19 @@
         <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -9005,19 +8999,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9037,19 +9031,19 @@
         <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9069,19 +9063,19 @@
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9101,19 +9095,19 @@
         <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9133,19 +9127,19 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9165,19 +9159,19 @@
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9197,19 +9191,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9229,19 +9223,19 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9261,19 +9255,19 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9293,19 +9287,19 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9325,19 +9319,19 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9357,19 +9351,19 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9389,19 +9383,19 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9421,19 +9415,19 @@
         <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9453,19 +9447,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9485,19 +9479,19 @@
         <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9517,19 +9511,19 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9549,19 +9543,19 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9581,19 +9575,19 @@
         <v>15</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9613,19 +9607,19 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9645,19 +9639,19 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9677,19 +9671,19 @@
         <v>3</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9709,19 +9703,19 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9741,19 +9735,19 @@
         <v>4</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9773,19 +9767,19 @@
         <v>4</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9805,19 +9799,19 @@
         <v>3</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9837,19 +9831,19 @@
         <v>3</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9869,19 +9863,19 @@
         <v>4</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9901,19 +9895,19 @@
         <v>4</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9933,19 +9927,19 @@
         <v>15</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9965,19 +9959,19 @@
         <v>1</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9997,19 +9991,19 @@
         <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="F233" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E233" s="2" t="s">
+      <c r="G233" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="G233" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -10029,19 +10023,19 @@
         <v>10</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10061,19 +10055,19 @@
         <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10093,19 +10087,19 @@
         <v>8</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10125,19 +10119,19 @@
         <v>9</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10157,19 +10151,19 @@
         <v>9</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10189,19 +10183,19 @@
         <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10221,19 +10215,19 @@
         <v>9</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10253,19 +10247,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10285,19 +10279,19 @@
         <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10317,19 +10311,19 @@
         <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10349,19 +10343,19 @@
         <v>10</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10381,19 +10375,19 @@
         <v>14</v>
       </c>
       <c r="C245" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10413,19 +10407,19 @@
         <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10445,19 +10439,19 @@
         <v>10</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10477,19 +10471,19 @@
         <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10509,19 +10503,19 @@
         <v>10</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10541,19 +10535,19 @@
         <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10573,19 +10567,19 @@
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10605,19 +10599,19 @@
         <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10637,19 +10631,19 @@
         <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10669,19 +10663,19 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10701,19 +10695,19 @@
         <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10733,19 +10727,19 @@
         <v>9</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10765,19 +10759,19 @@
         <v>10</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10797,19 +10791,19 @@
         <v>8</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10829,19 +10823,19 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10861,19 +10855,19 @@
         <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10893,19 +10887,19 @@
         <v>10</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10925,19 +10919,19 @@
         <v>8</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10957,19 +10951,19 @@
         <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10989,19 +10983,19 @@
         <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -11021,19 +11015,19 @@
         <v>10</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11053,19 +11047,19 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11085,19 +11079,19 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11117,19 +11111,19 @@
         <v>9</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11149,19 +11143,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11181,19 +11175,19 @@
         <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11213,19 +11207,19 @@
         <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11245,19 +11239,19 @@
         <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11277,19 +11271,19 @@
         <v>10</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11309,19 +11303,19 @@
         <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11341,19 +11335,19 @@
         <v>8</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11373,19 +11367,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11405,19 +11399,19 @@
         <v>14</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11437,19 +11431,19 @@
         <v>10</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11469,19 +11463,19 @@
         <v>8</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11501,19 +11495,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11533,19 +11527,19 @@
         <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11565,19 +11559,19 @@
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11597,19 +11591,19 @@
         <v>14</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11629,19 +11623,19 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11661,19 +11655,19 @@
         <v>8</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11693,19 +11687,19 @@
         <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11725,19 +11719,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11757,19 +11751,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11789,19 +11783,19 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11821,19 +11815,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11853,19 +11847,19 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11885,19 +11879,19 @@
         <v>8</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11917,19 +11911,19 @@
         <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11949,19 +11943,19 @@
         <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11981,19 +11975,19 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -12013,19 +12007,19 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12045,19 +12039,19 @@
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12077,19 +12071,19 @@
         <v>8</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12109,19 +12103,19 @@
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12141,19 +12135,19 @@
         <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12173,19 +12167,19 @@
         <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12205,19 +12199,19 @@
         <v>14</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12237,19 +12231,19 @@
         <v>8</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12269,19 +12263,19 @@
         <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12301,19 +12295,19 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12333,19 +12327,19 @@
         <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12365,19 +12359,19 @@
         <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12397,19 +12391,19 @@
         <v>14</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12429,19 +12423,19 @@
         <v>8</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12461,19 +12455,19 @@
         <v>8</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12493,19 +12487,19 @@
         <v>14</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12525,19 +12519,19 @@
         <v>14</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12557,19 +12551,19 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12589,19 +12583,19 @@
         <v>8</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12621,19 +12615,19 @@
         <v>8</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12653,19 +12647,19 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12685,19 +12679,19 @@
         <v>8</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12717,19 +12711,19 @@
         <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12749,19 +12743,19 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12781,19 +12775,19 @@
         <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12813,19 +12807,19 @@
         <v>9</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12845,19 +12839,19 @@
         <v>10</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12877,19 +12871,19 @@
         <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12909,19 +12903,19 @@
         <v>14</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12941,19 +12935,19 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12973,19 +12967,19 @@
         <v>8</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -13005,19 +12999,19 @@
         <v>14</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -13037,19 +13031,19 @@
         <v>8</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13069,19 +13063,19 @@
         <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13101,19 +13095,19 @@
         <v>8</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13133,19 +13127,19 @@
         <v>9</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13165,19 +13159,19 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13197,19 +13191,19 @@
         <v>8</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>15</v>
@@ -13229,19 +13223,19 @@
         <v>14</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>15</v>
@@ -13261,19 +13255,19 @@
         <v>9</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>15</v>
@@ -13293,19 +13287,19 @@
         <v>9</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>15</v>
@@ -13325,19 +13319,19 @@
         <v>14</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>15</v>
@@ -13357,19 +13351,19 @@
         <v>8</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>15</v>
@@ -13389,19 +13383,19 @@
         <v>14</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>15</v>
@@ -13431,7 +13425,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13439,50 +13433,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -13504,21 +13498,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13527,7 +13521,7 @@
         <v>2018</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
